--- a/data/credit_bond_all_2026-10-16.xlsx
+++ b/data/credit_bond_all_2026-10-16.xlsx
@@ -943,8 +943,12 @@
           <t>1.14 ~ 1.44</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>20.17</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -1171,8 +1175,12 @@
           <t>1.45 ~ 1.80</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>33.71</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.63</t>
@@ -1401,8 +1409,12 @@
           <t>1.70 ~ 2.20</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>36.85</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
@@ -1458,8 +1470,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -2095,8 +2111,12 @@
           <t>1.40 ~ 1.80</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>62.34</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -2347,7 +2367,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2549,8 +2569,12 @@
           <t>1.25 ~ 1.45</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>12.34</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>1.45</t>
@@ -2781,8 +2805,12 @@
           <t>1.24 ~ 1.44</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>14.34</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -3235,8 +3263,12 @@
           <t>2.00 ~ 2.50</t>
         </is>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>10.09</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>2.16</t>
@@ -3467,8 +3499,12 @@
           <t>1.40 ~ 1.80</t>
         </is>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>30.18</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -3756,8 +3792,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
           <t>4-</t>
@@ -3927,8 +3967,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>16.71</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -4157,8 +4201,12 @@
           <t>1.65 ~ 1.85</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>34.85</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -4385,8 +4433,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>23.18</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -4613,8 +4665,12 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>43.71</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -4670,7 +4726,9 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>2.8</v>
+      </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
@@ -5067,8 +5125,12 @@
           <t>1.14 ~ 1.44</t>
         </is>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>20.17</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -5293,8 +5355,12 @@
           <t>1.20 ~ 1.60</t>
         </is>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>21.18</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -5350,8 +5416,12 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -5519,8 +5589,12 @@
           <t>1.55 ~ 2.05</t>
         </is>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="H24" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>9.2</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -5749,8 +5823,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="H25" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>16.71</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>1.56</t>
@@ -5979,8 +6057,12 @@
           <t>1.35 ~ 1.58</t>
         </is>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="H26" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>24.18</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -6435,8 +6517,12 @@
           <t>1.50 ~ 2.10</t>
         </is>
       </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="H28" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>42.71</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -6493,7 +6579,7 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.71</v>
+        <v>2.7125</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
@@ -7123,8 +7209,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="H31" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>37.53</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -7181,7 +7271,7 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.93</v>
+        <v>3.925</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
@@ -7355,8 +7445,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>16.71</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>1.56</t>
@@ -7880,7 +7974,9 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>3.64</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
@@ -8055,8 +8151,12 @@
           <t>1.90 ~ 2.40</t>
         </is>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="H35" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>62.85</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -9476,7 +9576,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U41" s="3"/>
+      <c r="U41" s="4" t="n">
+        <v>5.17</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
@@ -9649,8 +9751,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+      <c r="H42" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>18.85</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t>1.59</t>
@@ -9881,8 +9987,12 @@
           <t>1.20 ~ 1.60</t>
         </is>
       </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+      <c r="H43" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>21.18</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -10341,8 +10451,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+      <c r="H45" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>16.71</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>1.56</t>
@@ -10573,8 +10687,12 @@
           <t>1.44 ~ 1.64</t>
         </is>
       </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+      <c r="H46" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>30.71</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
           <t>1.61</t>
@@ -10805,8 +10923,12 @@
           <t>1.25 ~ 1.46</t>
         </is>
       </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="H47" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>16.03</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
           <t>1.35</t>
@@ -11033,8 +11155,12 @@
           <t>1.14 ~ 1.44</t>
         </is>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="H48" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>20.17</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -11263,8 +11389,12 @@
           <t>1.30 ~ 1.48</t>
         </is>
       </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="H49" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>25.03</v>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -11493,8 +11623,12 @@
           <t>1.30 ~ 1.50</t>
         </is>
       </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="H50" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>35.18</v>
+      </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
           <t>1.50</t>
@@ -11717,8 +11851,12 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="H51" s="4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>109.85</v>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -11767,7 +11905,7 @@
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>2.71</v>
+        <v>1.44</v>
       </c>
       <c r="V51" s="4" t="n">
         <v>3.0</v>
@@ -11945,8 +12083,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+      <c r="H52" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>34.53</v>
+      </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -12177,8 +12319,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="H53" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>50.85</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
           <t>1.87</t>
@@ -12401,8 +12547,12 @@
           <t>1.30 ~ 2.30</t>
         </is>
       </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="H54" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>23.85</v>
+      </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
           <t>1.62</t>
@@ -12458,7 +12608,9 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U54" s="3"/>
+      <c r="U54" s="4" t="n">
+        <v>4.68</v>
+      </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
@@ -12635,8 +12787,12 @@
           <t>1.25 ~ 1.50</t>
         </is>
       </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+      <c r="H55" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>14.34</v>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>1.36</t>
@@ -12867,8 +13023,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="H56" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>35.85</v>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -13335,8 +13495,12 @@
           <t>1.14 ~ 1.44</t>
         </is>
       </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="H58" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>20.17</v>
+      </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -13626,7 +13790,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U59" s="3"/>
+      <c r="U59" s="4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
@@ -13793,8 +13959,12 @@
           <t>1.70 ~ 2.20</t>
         </is>
       </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="H60" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>49.85</v>
+      </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
           <t>1.89</t>
@@ -14245,8 +14415,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="H62" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>37.53</v>
+      </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -14303,7 +14477,7 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>4.07</v>
+        <v>4.0667</v>
       </c>
       <c r="V62" s="4" t="n">
         <v>4.0</v>
@@ -14469,8 +14643,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="H63" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>38.53</v>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -14527,7 +14705,7 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>3.04</v>
+        <v>3.042</v>
       </c>
       <c r="V63" s="4" t="n">
         <v>37.5</v>
@@ -14717,7 +14895,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6600</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -14983,10 +15161,10 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>4.3</v>
+        <v>5.0</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>1.7</v>
+        <v>3.0</v>
       </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
@@ -15149,7 +15327,9 @@
       <c r="E66" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F66" s="3"/>
+      <c r="F66" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="4" t="n">
         <v>0.2</v>
@@ -15377,8 +15557,12 @@
           <t>1.50 ~ 1.83</t>
         </is>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>43.85</v>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
@@ -15670,7 +15854,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U68" s="3"/>
+      <c r="U68" s="4" t="n">
+        <v>3.41</v>
+      </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
@@ -15859,7 +16045,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0700/--</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
@@ -16122,7 +16308,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U70" s="3"/>
+      <c r="U70" s="4" t="n">
+        <v>1.98</v>
+      </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
@@ -16295,8 +16483,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="H71" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>33.53</v>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>1.61</t>
@@ -16356,7 +16548,7 @@
         <v>4.0</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>1.45</v>
+        <v>1.446</v>
       </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
@@ -17193,8 +17385,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+      <c r="H75" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>45.2</v>
+      </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
           <t>2.21</t>
@@ -17655,8 +17851,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
+      <c r="H77" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>30.85</v>
+      </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -17712,7 +17912,9 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="U77" s="3"/>
+      <c r="U77" s="4" t="n">
+        <v>3.34</v>
+      </c>
       <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
@@ -17881,8 +18083,12 @@
           <t>1.60 ~ 2.00</t>
         </is>
       </c>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="H78" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>57.53</v>
+      </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -18335,8 +18541,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+      <c r="H80" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>76.85</v>
+      </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
           <t>2.22</t>
@@ -18559,8 +18769,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+      <c r="H81" s="4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>109.85</v>
+      </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
           <t>2.37</t>
@@ -19540,7 +19754,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U85" s="3"/>
+      <c r="U85" s="4" t="n">
+        <v>4.43</v>
+      </c>
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-10-16.xlsx
+++ b/data/credit_bond_all_2026-10-16.xlsx
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>3.98</v>
+        <v>3.9789</v>
       </c>
       <c r="V4" s="4" t="n">
         <v>1.67</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.0</v>
+        <v>5.07</v>
       </c>
       <c r="V23" s="4" t="n">
         <v>1.7</v>
@@ -7890,72 +7890,74 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26扬子G9</t>
+          <t>26中国平煤MTN010</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>10-16 19:00</t>
+          <t>10-19 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>246246.SH</t>
+          <t>102684083.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.43</v>
+        <v>2.0</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15.71</v>
+        <v>74.78</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26扬子G7</t>
+          <t>25中国平煤MTN010</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>1.99Y+N</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>2.0508</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司</t>
+          <t>中国平煤神马控股集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.23</t>
+          <t>C+ 31.15</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7965,12 +7967,12 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>10-16 16:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7979,17 +7981,17 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.17</v>
+        <v>3.17</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8000,23 +8002,23 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>河南省-平顶山市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子Y1]</t>
+          <t>发行人本期基础发行规模0亿元,发行金额上限10亿元,拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8026,12 +8028,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第五期)</t>
+          <t>中国平煤神马控股集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8041,64 +8043,60 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-20</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8106,147 +8104,153 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AZ34" s="3"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AZ34" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26江西文演MTN001</t>
+          <t>26扬子G9</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>10-16 18:00</t>
+          <t>10-16 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102690073.IB</t>
+          <t>246246.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.48</v>
+        <v>1.43</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>109.85</v>
+        <v>15.71</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>26扬子G7</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2.94Y</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1.6099</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>1.7000/--</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>南京扬子国资投资集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>C+ 30.23</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>10-16 16:00</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>江西文化演艺发展集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>D- 2.86</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>10-16 09:00</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>5.17</v>
+      </c>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.42%~2.52%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额5亿元,计划将募集资金全部用于偿还有息负债</t>
+          <t>本次债券募集资金用途为偿还到期的公司债券本金[23扬子Y1]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>江西银行股份有限公司,东兴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8256,12 +8260,12 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>江西文化演艺发展集团有限责任公司2026年度第一期中期票据</t>
+          <t>南京扬子国资投资集团有限责任公司2026年面向专业投资者公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8271,62 +8275,62 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
+          <t>2029-10-20</t>
         </is>
       </c>
       <c r="AK35" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>传媒</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>其他传媒</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他传媒</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>文化传媒</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -8336,7 +8340,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8349,14 +8353,12 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26日照能源MTN001</t>
+          <t>26江西文演MTN001</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8366,12 +8368,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102684063.IB</t>
+          <t>102690073.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8382,48 +8384,40 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>50.85</v>
+        <v>109.85</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>25日照能源MTN001</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>3.75Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.9000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>日照交通能源发展集团有限公司</t>
+          <t>江西文化演艺发展集团有限责任公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.31</t>
+          <t>D- 2.86</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8438,7 +8432,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8447,19 +8441,19 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>5.19</v>
+        <v>1.44</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>2.42%~2.52%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8470,17 +8464,17 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>山东省-日照市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金用于偿还发行人及子公司有息债务</t>
+          <t>发行人本次中期票据发行金额5亿元,计划将募集资金全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>江西银行股份有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8501,7 +8495,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>日照交通能源发展集团有限公司2026年度第一期中期票据</t>
+          <t>江西文化演艺发展集团有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8536,25 +8530,37 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ36" s="3"/>
-      <c r="AR36" s="3"/>
-      <c r="AS36" s="3"/>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr">
+        <is>
+          <t>传媒</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>其他传媒</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>其他传媒</t>
+        </is>
+      </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>文化传媒</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8564,7 +8570,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8578,13 +8584,13 @@
         </is>
       </c>
       <c r="AZ36" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26陕西交通MTN012(取消发行)</t>
+          <t>26日照能源MTN001</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8594,58 +8600,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>DY102684079.IB</t>
+          <t>102684063.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.01</t>
-        </is>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>50.85</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25陕西交控MTN001</t>
+          <t>25日照能源MTN001</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>8.33Y</t>
+          <t>3.75Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9716</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>陕西交通控股集团有限公司</t>
+          <t>日照交通能源发展集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 24.33</t>
+          <t>C+ 30.31</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8660,7 +8672,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -8668,37 +8680,41 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>陕西省</t>
+          <t>山东省-日照市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额20亿元,拟全部用于偿还即将到期的有息债务。</t>
+          <t>本期中期票据募集资金用于偿还发行人及子公司有息债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司</t>
+          <t>青岛银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8719,7 +8735,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>陕西交通控股集团有限公司2026年度第十二期中期票据(取消发行)</t>
+          <t>日照交通能源发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8729,7 +8745,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2036-10-19</t>
+          <t>2031-10-19</t>
         </is>
       </c>
       <c r="AK37" s="3" t="inlineStr">
@@ -8759,24 +8775,12 @@
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3"/>
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="3"/>
       <c r="AT37" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -8808,78 +8812,74 @@
         </is>
       </c>
       <c r="AZ37" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26杭安03</t>
+          <t>26陕西交通MTN012(取消发行)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>10-16 19:00</t>
+          <t>10-16 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>284181.SH</t>
+          <t>DY102684079.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>42.85</v>
-      </c>
+          <t>1.70 ~ 2.01</t>
+        </is>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26杭安02</t>
+          <t>25陕西交控MTN001</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>8.33Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6380</t>
+          <t>1.9716</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>杭州市安居集团有限公司</t>
+          <t>陕西交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C 27.81</t>
+          <t>C- 24.33</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8889,22 +8889,20 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>10-16 15:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="n">
-        <v>2.4</v>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
@@ -8913,7 +8911,7 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8924,23 +8922,23 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>陕西省</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金规模不超过4亿元(含4亿元),本期债券的募集资金扣除发行费用后,拟用于偿还有息负债。</t>
+          <t>本期中期票据发行金额20亿元,拟全部用于偿还即将到期的有息债务。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>招商银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8950,75 +8948,79 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>杭州市安居集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>陕西交通控股集团有限公司2026年度第十二期中期票据(取消发行)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2036-10-19</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9039,12 +9041,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ38" s="3"/>
+      <c r="AZ38" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26汕尾02</t>
+          <t>26杭安03</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9054,7 +9058,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>284265.SH</t>
+          <t>284181.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9068,48 +9072,48 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>49.85</v>
+        <v>42.85</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26汕尾01</t>
+          <t>26杭安02</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.87Y</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.8862</t>
+          <t>1.6380</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.9000/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>汕尾市投资控股有限公司</t>
+          <t>杭州市安居集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.85</t>
+          <t>C 27.81</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9132,37 +9136,39 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>广东省-汕尾市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于偿还回售公司债券本金、0.70亿元用于科技创新领域出资、0.30亿元用于偿还有息债务。[23汕尾02,24汕尾01]</t>
+          <t>本期债券拟募集资金规模不超过4亿元(含4亿元),本期债券的募集资金扣除发行费用后,拟用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,国泰海通证券股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9183,7 +9189,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>汕尾市投资控股有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>杭州市安居集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9219,27 +9225,27 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9272,7 +9278,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26狮桥04</t>
+          <t>26汕尾02</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9282,62 +9288,62 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>246188.SH</t>
+          <t>284265.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.90</t>
+          <t>1.70 ~ 2.20</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>64.53</v>
+        <v>49.85</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26狮桥03</t>
+          <t>26汕尾01</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1.76Y</t>
+          <t>4.87Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.9732</t>
+          <t>1.8862</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9000/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>狮桥融资租赁(中国)有限公司</t>
+          <t>汕尾市投资控股有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.04</t>
+          <t>C+ 31.85</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9364,37 +9370,33 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z40" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-汕尾市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除相关发行费用后,拟将不超过人民币5亿元用于偿还公司债券本金。[25狮桥03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于偿还回售公司债券本金、0.70亿元用于科技创新领域出资、0.30亿元用于偿还有息债务。[23汕尾02,24汕尾01]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,中信证券股份有限公司,中银国际证券股份有限公司,申港证券股份有限公司</t>
+          <t>五矿证券有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9415,17 +9417,17 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>狮桥融资租赁(中国)有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>汕尾市投资控股有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2028-10-20</t>
+          <t>2031-10-20</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -9446,32 +9448,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9504,17 +9506,17 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26宿迁新城PPN002</t>
+          <t>26狮桥04</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>10-16 18:00</t>
+          <t>10-16 19:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>032690047.IB</t>
+          <t>246188.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -9523,55 +9525,53 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.90</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>37.53</v>
+        <v>64.53</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26宿新01</t>
+          <t>26狮桥03</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.61Y</t>
+          <t>1.76Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6642</t>
+          <t>1.9732</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/1.6800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司</t>
+          <t>狮桥融资租赁(中国)有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 35.07</t>
+          <t>D+ 7.04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9581,60 +9581,60 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 15:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="U41" s="4" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>2.0</v>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z41" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行金额3.00亿元募集资金拟用于偿还发行人存量债务融资工具本金[26宿迁新城SCP002]</t>
+          <t>本期债券的募集资金扣除相关发行费用后,拟将不超过人民币5亿元用于偿还公司债券本金。[25狮桥03]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,苏州银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>国投证券股份有限公司,中信证券股份有限公司,中银国际证券股份有限公司,申港证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9644,68 +9644,68 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>宿迁市新城控股集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>狮桥融资租赁(中国)有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2028-10-20</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9738,64 +9738,74 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26阜阳城南PPN002</t>
+          <t>26宿迁新城PPN002</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
-        </is>
-      </c>
-      <c r="C42" s="3"/>
+          <t>10-16 18:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>032690047.IB</t>
+        </is>
+      </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>37.53</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26阜阳城南PPN001</t>
+          <t>26宿新01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.43Y</t>
+          <t>2.61Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.6777</t>
+          <t>1.6642</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6800</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>阜阳市城南新区建设投资有限公司</t>
+          <t>宿迁市新城控股集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.68</t>
+          <t>B- 35.07</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9810,19 +9820,19 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>1.7</v>
+        <v>4.07</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>1.53</v>
+        <v>2.0</v>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
@@ -9831,28 +9841,28 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向债务融资工具拟发行3亿元,募集资金拟全部用于偿还存量债务融资工具[23阜阳城南MTN001]</t>
+          <t>本期拟发行金额3.00亿元募集资金拟用于偿还发行人存量债务融资工具本金[26宿迁新城SCP002]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>徽商银行股份有限公司,国信证券股份有限公司</t>
+          <t>江苏银行股份有限公司,苏州银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9873,7 +9883,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>阜阳市城南新区建设投资有限公司2026年度第二期定向债务融资工具</t>
+          <t>宿迁市新城控股集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9883,17 +9893,13 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2029-10-20</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2028-10-19</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9903,17 +9909,17 @@
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
@@ -9958,57 +9964,61 @@
       </c>
       <c r="AY42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ42" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AZ42" s="3"/>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>中科转债</t>
+          <t>26阜阳城南PPN002</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>10-16 15:00</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>123289.SZ</t>
-        </is>
-      </c>
+          <t>10-19 18:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G43" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="n">
-        <v>0.2</v>
+        <v>1.73</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>-122.67</v>
+        <v>46.26</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>26阜阳城南PPN001</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>2.43Y</t>
+        </is>
+      </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6777</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -10018,12 +10028,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>北京中科润宇环保科技股份有限公司</t>
+          <t>阜阳市城南新区建设投资有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C+ 30.68</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10033,56 +10043,60 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:15</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>1.53</v>
+      </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
           <t>6+</t>
         </is>
       </c>
-      <c r="X43" s="3"/>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券募集资金总额不超过人民币100,000.00万元(含100,000.00万元),扣除发行费用后,募集资金净额拟投入常宁市生活垃圾焚烧发电项目、绵阳市第三生活垃圾焚烧发电项目(江油市)(一期工程)、石家庄中科新能源有限公司热力生产提升工程、藤县低碳循环经济产业园--生活垃圾焚烧发电项目、补充流动资金及偿还银行贷款</t>
+          <t>发行人本次定向债务融资工具拟发行3亿元,募集资金拟全部用于偿还存量债务融资工具[23阜阳城南MTN001]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>徽商银行股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -10092,22 +10106,22 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>2026年北京中科润宇环保科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>阜阳市城南新区建设投资有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2032-10-16</t>
+          <t>2029-10-20</t>
         </is>
       </c>
       <c r="AK43" s="3" t="inlineStr">
@@ -10117,54 +10131,54 @@
       </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM43" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AO43" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ43" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR43" s="3" t="inlineStr">
-        <is>
-          <t>环保</t>
-        </is>
-      </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>固废治理</t>
-        </is>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>环保工程及服务</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10182,65 +10196,57 @@
       </c>
       <c r="AY43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AZ43" s="3"/>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AZ43" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26路桥02</t>
+          <t>中科转债</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>10-16 19:00</t>
+          <t>10-16 15:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>246252.SH</t>
+          <t>123289.SZ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
+      <c r="F44" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="4" t="n">
-        <v>1.75</v>
+        <v>0.2</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>36.85</v>
+        <v>-122.67</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>26路桥01</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>4.48Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.6969</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -10250,12 +10256,12 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>厦门路桥建设集团有限公司</t>
+          <t>北京中科润宇环保科技股份有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 13.93</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10265,7 +10271,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>10-16 15:00</t>
+          <t>10-16 09:15</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10275,44 +10281,46 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="n">
-        <v>3.41</v>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X44" s="3"/>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z44" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金在扣除发行费用后,拟全部用于偿还“23路桥02”公司债券到期本金[23路桥02]</t>
+          <t>本次发行可转换公司债券募集资金总额不超过人民币100,000.00万元(含100,000.00万元),扣除发行费用后,募集资金净额拟投入常宁市生活垃圾焚烧发电项目、绵阳市第三生活垃圾焚烧发电项目(江油市)(一期工程)、石家庄中科新能源有限公司热力生产提升工程、藤县低碳循环经济产业园--生活垃圾焚烧发电项目、补充流动资金及偿还银行贷款</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,华福证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10322,12 +10330,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>厦门路桥建设集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>2026年北京中科润宇环保科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10337,10 +10345,14 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-10-20</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2032-10-16</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10348,7 +10360,7 @@
       </c>
       <c r="AM44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AN44" s="3" t="inlineStr">
@@ -10358,32 +10370,32 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>环保</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>固废治理</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>环保工程及服务</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10416,70 +10428,72 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26中国平煤MTN010</t>
+          <t>26路桥02</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>10-19 18:00</t>
+          <t>10-16 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102684083.IB</t>
+          <t>246252.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>10.0</v>
-      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>36.85</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>25中国平煤MTN010</t>
+          <t>26路桥01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>1.99Y+N</t>
+          <t>4.48Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2.0508</t>
+          <t>1.6969</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>2.0700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>中国平煤神马控股集团有限公司</t>
+          <t>厦门路桥建设集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.15</t>
+          <t>C- 13.93</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10489,12 +10503,12 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -10502,18 +10516,16 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U45" s="3"/>
+      <c r="U45" s="4" t="n">
+        <v>3.41</v>
+      </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>2.20%~2.30%</t>
-        </is>
-      </c>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X45" s="3"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10522,23 +10534,23 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>河南省-平顶山市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>发行人本期基础发行规模0亿元,发行金额上限10亿元,拟全部用于偿还有息债务</t>
+          <t>本期债券募集资金在扣除发行费用后,拟全部用于偿还“23路桥02”公司债券到期本金[23路桥02]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,华夏银行股份有限公司</t>
+          <t>兴业证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10548,12 +10560,12 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>中国平煤神马控股集团有限公司2026年度第十期中期票据</t>
+          <t>厦门路桥建设集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10563,18 +10575,18 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2028-10-20</t>
+          <t>2031-10-20</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t/>
         </is>
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10584,32 +10596,32 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10624,22 +10636,20 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AZ45" s="4" t="n">
-        <v>0.02</v>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AZ45" s="3"/>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
@@ -13158,7 +13168,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26中石油MTN001(科创债)</t>
+          <t>26中建一局SCP007</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13168,64 +13178,64 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>102684072.IB</t>
+          <t>012682464.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.25 ~ 1.45</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16.71</v>
+        <v>12.34</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>24中石油MTN001</t>
+          <t>26中建一局SCP003</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>98D</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.5608</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>1.4800/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司</t>
+          <t>中国建筑一局(集团)有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 20.69</t>
+          <t>B- 41.03</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13240,7 +13250,7 @@
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
@@ -13249,17 +13259,19 @@
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="V57" s="3"/>
+        <v>1.42</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -13267,11 +13279,7 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z57" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -13279,23 +13287,23 @@
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟募集资金50亿元,募集资金最终用于发行人科技创新及主营业务生产经营</t>
+          <t>发行人本期债务融资工具发行金额5亿元，所募集资金拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国建设银行股份有限公司,中国农业银行股份有限公司,招商银行股份有限公司</t>
+          <t>渤海银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG57" s="3" t="inlineStr">
@@ -13305,7 +13313,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司2026年度第一期科技创新债券</t>
+          <t>中国建筑一局(集团)有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13315,7 +13323,7 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
@@ -13341,27 +13349,27 @@
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>其他石油石化</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13389,12 +13397,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ57" s="3"/>
+      <c r="AZ57" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26中建一局SCP007</t>
+          <t>26东航SCP006</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13404,64 +13414,64 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>012682464.IB</t>
+          <t>012682470.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.2Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.45</t>
+          <t>1.25 ~ 1.50</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12.34</v>
+        <v>14.34</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26中建一局SCP003</t>
+          <t>26东航SCP003</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>98D</t>
+          <t>174D</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.4545</t>
+          <t>1.4680</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.4800/--</t>
+          <t>1.4600/1.4600</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>中国建筑一局(集团)有限公司</t>
+          <t>中国东方航空集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>B- 41.03</t>
+          <t>B- 45.61</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13476,7 +13486,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
@@ -13485,19 +13495,19 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="V58" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.41%~1.45%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -13508,17 +13518,17 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额5亿元，所募集资金拟用于偿还有息债务</t>
+          <t>本期超短期融资券发行金额为10亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,杭州银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -13529,7 +13539,7 @@
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
@@ -13539,7 +13549,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>中国建筑一局(集团)有限公司2026年度第七期超短期融资券</t>
+          <t>中国东方航空集团有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13549,7 +13559,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13575,27 +13585,27 @@
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13630,7 +13640,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26东航SCP006</t>
+          <t>26桂投资MTN002A(取消发行)</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13640,64 +13650,58 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>012682470.IB</t>
+          <t>DY102684074.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>0.2Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>14.34</v>
-      </c>
+          <t>1.70 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26东航SCP003</t>
+          <t>25桂投资MTN004B</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>174D</t>
+          <t>3.60Y+N</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.4680</t>
+          <t>1.9800</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.4600/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司</t>
+          <t>广西投资集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>B- 45.61</t>
+          <t>C 28.84</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13712,7 +13716,7 @@
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
@@ -13720,20 +13724,16 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U59" s="4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.41%~1.45%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13744,28 +13744,28 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金</t>
+          <t>发行待偿还余额不超过5亿元的有息债务，募集资金全部用于发行人本部到期的短期流贷</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司2026年度第六期超短期融资券</t>
+          <t>广西投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13811,27 +13811,27 @@
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13846,12 +13846,12 @@
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX59" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY59" s="3" t="inlineStr">
@@ -13860,13 +13860,13 @@
         </is>
       </c>
       <c r="AZ59" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26桂投资MTN002A(取消发行)</t>
+          <t>26湖州城投MTN010</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13876,43 +13876,49 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>DY102684074.IB</t>
+          <t>102690075.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>23.85</v>
+      </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>25桂投资MTN004B</t>
+          <t>24湖州城投MTN004(项目收益)</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>3.60Y+N</t>
+          <t>3.05Y+5.00Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.9800</t>
+          <t>1.6182</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -13922,12 +13928,12 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司</t>
+          <t>湖州市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C 28.84</t>
+          <t>C- 20.74</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13937,7 +13943,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 14:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -13950,16 +13956,18 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U60" s="3"/>
+      <c r="U60" s="4" t="n">
+        <v>4.68</v>
+      </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -13967,20 +13975,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z60" s="3"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>发行待偿还余额不超过5亿元的有息债务，募集资金全部用于发行人本部到期的短期流贷</t>
+          <t>发行人本期中期票据拟发行6.00亿元，扣除发行费用后，全部用于偿还公司本部回售的债务融资工具本金【23 湖州城投MTN002】</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,广西北部湾银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -14001,7 +14013,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司2026年度第二期中期票据(品种一)(取消发行)</t>
+          <t>湖州市城市投资发展集团有限公司2026年度第十期中期票据</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14011,60 +14023,64 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK60" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
           <t>2029-10-19</t>
         </is>
       </c>
-      <c r="AK60" s="3"/>
-      <c r="AL60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AM60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AO60" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ60" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR60" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS60" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
-      <c r="AU60" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -14077,7 +14093,7 @@
       </c>
       <c r="AX60" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY60" s="3" t="inlineStr">
@@ -14085,14 +14101,12 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ60" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ60" s="3"/>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26湖州城投MTN010</t>
+          <t>26中海油租MTN002</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14102,64 +14116,64 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>102690075.IB</t>
+          <t>102684082.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.44 ~ 1.64</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>23.85</v>
+        <v>30.71</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>24湖州城投MTN004(项目收益)</t>
+          <t>26中海油租MTN001</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>3.05Y+5.00Y</t>
+          <t>2.89Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.6182</t>
+          <t>1.6254</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>湖州市城市投资发展集团有限公司</t>
+          <t>中海油国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 20.74</t>
+          <t>B+ 58.75</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14169,12 +14183,12 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>10-16 14:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
@@ -14183,17 +14197,19 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="V61" s="3"/>
+        <v>1.41</v>
+      </c>
+      <c r="V61" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -14201,24 +14217,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z61" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟发行6.00亿元，扣除发行费用后，全部用于偿还公司本部回售的债务融资工具本金【23 湖州城投MTN002】</t>
+          <t>本期中期票据发行规模10亿元,用于偿还到期债券[26中海油租SCP002]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,杭州银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
@@ -14229,7 +14241,7 @@
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
@@ -14239,7 +14251,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>湖州市城市投资发展集团有限公司2026年度第十期中期票据</t>
+          <t>中海油国际融资租赁有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14249,14 +14261,10 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK61" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-19</t>
+        </is>
+      </c>
+      <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -14274,37 +14282,37 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t/>
         </is>
       </c>
       <c r="AV61" s="3" t="inlineStr">
@@ -14314,7 +14322,7 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
@@ -14327,12 +14335,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ61" s="3"/>
+      <c r="AZ61" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26中海油租MTN002</t>
+          <t>26园博园MTN004</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14342,7 +14352,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>102684082.IB</t>
+          <t>102684076.IB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -14351,55 +14361,55 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.44 ~ 1.64</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>30.71</v>
+        <v>43.71</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26中海油租MTN001</t>
+          <t>26园博园MTN003</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.89Y</t>
+          <t>2.83Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.6254</t>
+          <t>1.7168</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/1.6200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司</t>
+          <t>江苏园博园建设开发有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.75</t>
+          <t>C- 17.54</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14414,7 +14424,7 @@
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
@@ -14423,40 +14433,38 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元,用于偿还到期债券[26中海油租SCP002]</t>
+          <t>发行人本期发行金额为3.00亿元,拟全部用于偿还发行人即将到期的债务融资工具本金[25园博园CP004]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中信银行股份有限公司</t>
+          <t>苏州银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14467,7 +14475,7 @@
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
@@ -14477,7 +14485,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司2026年度第二期中期票据</t>
+          <t>江苏园博园建设开发有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14508,32 +14516,32 @@
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14561,14 +14569,12 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ62" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ62" s="3"/>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26园博园MTN004</t>
+          <t>26中化股SCP015</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14578,64 +14584,64 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>102684076.IB</t>
+          <t>012682455.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.14 ~ 1.44</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>43.71</v>
+        <v>20.17</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26园博园MTN003</t>
+          <t>21中化04</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2.83Y</t>
+          <t>44D</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.7168</t>
+          <t>1.4365</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/1.4500</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>江苏园博园建设开发有限公司</t>
+          <t>中国中化股份有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C- 17.54</t>
+          <t>A- 63.01</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14645,7 +14651,7 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 11:00</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -14659,49 +14665,51 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V63" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.40%~1.44%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额为3.00亿元,拟全部用于偿还发行人即将到期的债务融资工具本金[25园博园CP004]</t>
+          <t>发行人本期超短期融资券的发行规模为15亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>苏州银行股份有限公司,南京银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG63" s="3" t="inlineStr">
@@ -14711,7 +14719,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>江苏园博园建设开发有限公司2026年度第四期中期票据</t>
+          <t>中国中化股份有限公司2026年度第十五期超短期融资券</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14721,7 +14729,7 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
@@ -14742,32 +14750,32 @@
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>石油化工与贸易</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>旅游综合</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -14800,7 +14808,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP015</t>
+          <t>26厦钨MTN002(科创债)</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14810,64 +14818,64 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>012682455.IB</t>
+          <t>102684080.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.14 ~ 1.44</t>
+          <t>1.45 ~ 1.80</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20.17</v>
+        <v>33.71</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>21中化04</t>
+          <t>26厦钨MTN001(科创债)</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>44D</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.4365</t>
+          <t>1.6639</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.4500</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司</t>
+          <t>厦门钨业股份有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>A- 63.01</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14877,7 +14885,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>10-16 11:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -14891,19 +14899,19 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>1.0</v>
+        <v>4.74</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>1.0</v>
+        <v>2.3</v>
       </c>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.40%~1.44%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -14914,28 +14922,28 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券的发行规模为15亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
+          <t>发行人本期科技创新债券发行金额为5亿元,拟全部用于偿还发行人本部银行贷款(部分贷款为提前还款)。</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -14945,7 +14953,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第十五期超短期融资券</t>
+          <t>厦门钨业股份有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -14955,7 +14963,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
@@ -14981,27 +14989,27 @@
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>石油化工与贸易</t>
+          <t>稀有稀土金属</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>稀有金属</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15034,7 +15042,7 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26厦钨MTN002(科创债)</t>
+          <t>26信达SCP001</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15044,12 +15052,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>102684080.IB</t>
+          <t>012682453.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.2Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -15060,48 +15068,48 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.80</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>33.71</v>
+        <v>62.34</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>26厦钨MTN001(科创债)</t>
+          <t>25信达MTN001</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>1.20Y+N</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.6639</t>
+          <t>2.5715</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>2.7500/--</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>厦门钨业股份有限公司</t>
+          <t>厦门信达股份有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 10.09</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15116,7 +15124,7 @@
       </c>
       <c r="S65" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
@@ -15125,24 +15133,22 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="V65" s="4" t="n">
-        <v>2.3</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.77%~1.81%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z65" s="3"/>
@@ -15153,18 +15159,18 @@
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券发行金额为5亿元,拟全部用于偿还发行人本部银行贷款(部分贷款为提前还款)。</t>
+          <t>本期超短期融资券拟发行规模为5亿元,募集资金拟用于偿还发行人银行借款</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -15179,7 +15185,7 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>厦门钨业股份有限公司2026年度第二期科技创新债券</t>
+          <t>厦门信达股份有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
@@ -15189,7 +15195,7 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
@@ -15215,27 +15221,27 @@
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>综合贸易零售</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>稀有稀土金属</t>
+          <t>综合贸易零售</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -15263,12 +15269,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ65" s="3"/>
+      <c r="AZ65" s="4" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26信达SCP001</t>
+          <t>26华能集SCP008</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15278,64 +15286,64 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>012682453.IB</t>
+          <t>012682452.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>0.2Y</t>
+          <t>0.35Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.25 ~ 1.46</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>62.34</v>
+        <v>16.03</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>25信达MTN001</t>
+          <t>26华能集SCP007</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>1.20Y+N</t>
+          <t>69D</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>2.5715</t>
+          <t>1.4250</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>2.7500/--</t>
+          <t>1.4300/1.4200</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>厦门信达股份有限公司</t>
+          <t>中国华能集团有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C- 10.09</t>
+          <t>B- 40.61</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15350,7 +15358,7 @@
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
@@ -15359,38 +15367,40 @@
         </is>
       </c>
       <c r="U66" s="4" t="n">
+        <v>1.2667</v>
+      </c>
+      <c r="V66" s="4" t="n">
         <v>1.0</v>
       </c>
-      <c r="V66" s="3"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.81%</t>
+          <t>1.41%~1.45%</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟发行规模为5亿元,募集资金拟用于偿还发行人银行借款</t>
+          <t>本期债务融资工具拟募集资金30亿元,用于偿还公司本部到期债务</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
@@ -15401,7 +15411,7 @@
       </c>
       <c r="AF66" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG66" s="3" t="inlineStr">
@@ -15411,7 +15421,7 @@
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>厦门信达股份有限公司2026年度第一期超短期融资券</t>
+          <t>中国华能集团有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15421,7 +15431,7 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="AK66" s="3"/>
@@ -15447,27 +15457,27 @@
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>综合贸易零售</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>综合贸易零售</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
@@ -15495,14 +15505,12 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ66" s="4" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="AZ66" s="3"/>
     </row>
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26华能集SCP008</t>
+          <t>26广州净水SCP003</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15512,64 +15520,64 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>012682452.IB</t>
+          <t>012682458.IB</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>0.35Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>30.0</v>
+        <v>3.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>30.0</v>
+        <v>3.0</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.46</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16.03</v>
+        <v>30.18</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26华能集SCP007</t>
+          <t>26广州净水SCP002</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>69D</t>
+          <t>200D</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.4250</t>
+          <t>1.4897</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>1.4300/1.4200</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>中国华能集团有限公司</t>
+          <t>广州市净水有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>B- 40.61</t>
+          <t>C- 16.67</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15584,7 +15592,7 @@
       </c>
       <c r="S67" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="T67" s="3" t="inlineStr">
@@ -15593,19 +15601,19 @@
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>1.2667</v>
+        <v>4.2333</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>1.0</v>
+        <v>1.5</v>
       </c>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.41%~1.45%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
@@ -15616,17 +15624,17 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具拟募集资金30亿元,用于偿还公司本部到期债务</t>
+          <t>本期发行金额3亿元超短期融资券扣除承销费用后全部用于补充营运资金</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
@@ -15637,7 +15645,7 @@
       </c>
       <c r="AF67" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG67" s="3" t="inlineStr">
@@ -15647,7 +15655,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>中国华能集团有限公司2026年度第八期超短期融资券</t>
+          <t>广州市净水有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15657,7 +15665,7 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-07-16</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
@@ -15683,7 +15691,7 @@
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
@@ -15693,17 +15701,17 @@
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU67" s="3" t="inlineStr">
@@ -15731,12 +15739,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ67" s="3"/>
+      <c r="AZ67" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26广州净水SCP003</t>
+          <t>26中兵物资SCP003</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15746,7 +15756,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>012682458.IB</t>
+          <t>012682457.IB</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -15755,55 +15765,55 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.35 ~ 1.58</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>30.18</v>
+        <v>24.18</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>26广州净水SCP002</t>
+          <t>26中兵物资SCP002</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>231D</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>1.4897</t>
+          <t>1.5124</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>C- 16.67</t>
+          <t>B- 36.67</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15818,7 +15828,7 @@
       </c>
       <c r="S68" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T68" s="3" t="inlineStr">
@@ -15827,14 +15837,12 @@
         </is>
       </c>
       <c r="U68" s="4" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="V68" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
@@ -15850,17 +15858,17 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额3亿元超短期融资券扣除承销费用后全部用于补充营运资金</t>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司</t>
+          <t>平安银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
@@ -15871,7 +15879,7 @@
       </c>
       <c r="AF68" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG68" s="3" t="inlineStr">
@@ -15881,7 +15889,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>广州市净水有限公司2026年度第三期超短期融资券</t>
+          <t>中国兵工物资集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -15922,22 +15930,22 @@
       </c>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
@@ -15965,81 +15973,79 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ68" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ68" s="3"/>
     </row>
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26浙国贸SCP004</t>
+          <t>26九安医疗MTN004(科创债)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>10-16 18:00</t>
+          <t>10-16 19:00</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>012682460.IB</t>
+          <t>102684077.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>4.0</v>
+        <v>6.3</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>4.0</v>
+        <v>6.3</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.60 ~ 2.00</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>22.18</v>
+        <v>57.53</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>24浙国贸MTN001</t>
+          <t>26九安医疗MTN003(科创债)</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>157D</t>
+          <t>1.79Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.4886</t>
+          <t>1.6591</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>浙江省国际贸易集团有限公司</t>
+          <t>天津九安医疗电子股份有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C 27.57</t>
+          <t>D 4.28</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16054,7 +16060,7 @@
       </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T69" s="3" t="inlineStr">
@@ -16063,17 +16069,19 @@
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V69" s="3"/>
+        <v>1.0159</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -16081,31 +16089,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z69" s="3"/>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额4亿元，募集资金拟用于偿还发行人即将到期的债务融资工具本金[26浙国贸SCP001]</t>
+          <t>募集资金拟全部用于偿还发行人本部即将到期的债务融资工具本金及银行借款【26九安医疗SCP001(科创债)】</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>渤海银行股份有限公司,上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司,招商银行股份有限公司,上海银行股份有限公司,中国银行股份有限公司,北京银行股份有限公司,天津银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG69" s="3" t="inlineStr">
@@ -16115,7 +16127,7 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>浙江省国际贸易集团有限公司2026年度第四期超短期融资券</t>
+          <t>天津九安医疗电子股份有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -16125,7 +16137,7 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
+          <t>2028-10-19</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
@@ -16136,7 +16148,7 @@
       </c>
       <c r="AM69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AN69" s="3" t="inlineStr">
@@ -16151,27 +16163,27 @@
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>医疗器械制造</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>医疗器械制造</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -16199,12 +16211,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ69" s="3"/>
+      <c r="AZ69" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP003</t>
+          <t>26中交投MTN004B</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16214,64 +16228,64 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>012682457.IB</t>
+          <t>102684062.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.58</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>24.18</v>
+        <v>42.71</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP002</t>
+          <t>交投YK02</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>231D</t>
+          <t>3.01Y+N</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.5124</t>
+          <t>1.6545</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>--/1.4700</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>中交投资有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>B- 36.67</t>
+          <t>C- 18.43</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16281,12 +16295,12 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 15:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T70" s="3" t="inlineStr">
@@ -16295,17 +16309,17 @@
         </is>
       </c>
       <c r="U70" s="4" t="n">
-        <v>1.9</v>
+        <v>2.71</v>
       </c>
       <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16313,7 +16327,11 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z70" s="3"/>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA70" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -16321,18 +16339,18 @@
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金</t>
+          <t>本期中期票据基础发行金额为0亿元，发行金额上限为12.00亿元，拟全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,浙商银行股份有限公司</t>
+          <t>申万宏源证券有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16347,7 +16365,7 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第三期超短期融资券</t>
+          <t>中交投资有限公司2026年度第四期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
@@ -16357,7 +16375,7 @@
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK70" s="3"/>
@@ -16383,27 +16401,27 @@
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16418,12 +16436,12 @@
       </c>
       <c r="AW70" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX70" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY70" s="3" t="inlineStr">
@@ -16436,74 +16454,74 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26九安医疗MTN004(科创债)</t>
+          <t>26晋城国资MTN005</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>10-16 19:00</t>
+          <t>10-16 18:00</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102684077.IB</t>
+          <t>102684064.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>6.3</v>
+        <v>8.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>6.3</v>
+        <v>8.0</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
+          <t>1.50 ~ 1.83</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>57.53</v>
+        <v>43.85</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26九安医疗MTN003(科创债)</t>
+          <t>26晋城01</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>1.79Y</t>
+          <t>2.52Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.6591</t>
+          <t>1.6649</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>天津九安医疗电子股份有限公司</t>
+          <t>晋城市国有资本投资运营有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>D 4.28</t>
+          <t>C+ 30.53</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16513,12 +16531,12 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 14:00</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="T71" s="3" t="inlineStr">
@@ -16527,44 +16545,40 @@
         </is>
       </c>
       <c r="U71" s="4" t="n">
-        <v>1.0159</v>
+        <v>1.7625</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>1.0</v>
+        <v>1.28</v>
       </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z71" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山西省-晋城市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>募集资金拟全部用于偿还发行人本部即将到期的债务融资工具本金及银行借款【26九安医疗SCP001(科创债)】</t>
+          <t>发行人本期中期票据基础发行规模为0亿元，发行金额上限为人民币8亿元，拟全部用于偿还发行人本部有息债务[25晋城国资CP001,23晋城国资MTN003]</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,上海浦东发展银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司,招商银行股份有限公司,上海银行股份有限公司,中国银行股份有限公司,北京银行股份有限公司,天津银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
@@ -16575,7 +16589,7 @@
       </c>
       <c r="AF71" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG71" s="3" t="inlineStr">
@@ -16585,7 +16599,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>天津九安医疗电子股份有限公司2026年度第四期科技创新债券</t>
+          <t>晋城市国有资本投资运营有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16595,10 +16609,14 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
-        </is>
-      </c>
-      <c r="AK71" s="3"/>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK71" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL71" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -16606,77 +16624,75 @@
       </c>
       <c r="AM71" s="3" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX71" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY71" s="3" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="AO71" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ71" s="3" t="inlineStr">
-        <is>
-          <t>医药制造</t>
-        </is>
-      </c>
-      <c r="AR71" s="3" t="inlineStr">
-        <is>
-          <t>医疗器械制造</t>
-        </is>
-      </c>
-      <c r="AS71" s="3" t="inlineStr">
-        <is>
-          <t>医疗器械制造</t>
-        </is>
-      </c>
-      <c r="AT71" s="3" t="inlineStr">
-        <is>
-          <t>医疗器械</t>
-        </is>
-      </c>
-      <c r="AU71" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV71" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW71" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX71" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY71" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AZ71" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ71" s="3"/>
     </row>
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26中交投MTN004B</t>
+          <t>26宿迁交通MTN003</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16686,64 +16702,64 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>102684062.IB</t>
+          <t>102684073.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>6.0</v>
+        <v>3.36</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>8.0</v>
+        <v>3.36</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>42.71</v>
+        <v>35.85</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>交投YK02</t>
+          <t>25宿迁交通MTN003</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>3.01Y+N</t>
+          <t>3.82Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.6545</t>
+          <t>1.6880</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>--/1.6600</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司</t>
+          <t>宿迁市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C- 18.43</t>
+          <t>C- 16.38</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16753,12 +16769,12 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>10-16 15:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T72" s="3" t="inlineStr">
@@ -16767,42 +16783,40 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="V72" s="3"/>
+        <v>3.8393</v>
+      </c>
+      <c r="V72" s="4" t="n">
+        <v>1.24</v>
+      </c>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z72" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行金额为0亿元，发行金额上限为12.00亿元，拟全部用于偿还发行人有息债务。</t>
+          <t>发行人本期债务融资工具募集资金3.36亿元,拟全部用于偿还存量债务融资工具本金[24宿迁交通MTN005]</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,招商银行股份有限公司</t>
+          <t>南京银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
@@ -16813,7 +16827,7 @@
       </c>
       <c r="AF72" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG72" s="3" t="inlineStr">
@@ -16823,7 +16837,7 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司2026年度第四期中期票据(品种二)</t>
+          <t>宿迁市交通产业集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16833,10 +16847,14 @@
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
-        </is>
-      </c>
-      <c r="AK72" s="3"/>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK72" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL72" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -16854,27 +16872,27 @@
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
@@ -16894,12 +16912,12 @@
       </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX72" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY72" s="3" t="inlineStr">
@@ -16907,12 +16925,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ72" s="3"/>
+      <c r="AZ72" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26晋城国资MTN005</t>
+          <t>26国新保理SCP008</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -16922,64 +16942,64 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>102684064.IB</t>
+          <t>012682465.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>8.0</v>
+        <v>11.8</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>8.0</v>
+        <v>11.8</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.83</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>43.85</v>
+        <v>35.18</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>26晋城01</t>
+          <t>25国保02</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2.52Y</t>
+          <t>280D</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.6649</t>
+          <t>1.5232</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>晋城市国有资本投资运营有限公司</t>
+          <t>国新商业保理有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.53</t>
+          <t>B- 41.35</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -16989,12 +17009,12 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>10-16 14:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T73" s="3" t="inlineStr">
@@ -17002,52 +17022,48 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U73" s="4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V73" s="4" t="n">
-        <v>1.28</v>
-      </c>
+      <c r="U73" s="3"/>
+      <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>山西省-晋城市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模为0亿元，发行金额上限为人民币8亿元，拟全部用于偿还发行人本部有息债务[25晋城国资CP001,23晋城国资MTN003]</t>
+          <t>本次发行11.8亿元拟用于偿还有息负债[26国新保理SCP001]</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,中信银行股份有限公司</t>
+          <t>平安银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG73" s="3" t="inlineStr">
@@ -17057,7 +17073,7 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>晋城市国有资本投资运营有限公司2026年度第五期中期票据</t>
+          <t>国新商业保理有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -17067,14 +17083,10 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK73" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="AK73" s="3"/>
       <c r="AL73" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -17092,32 +17104,28 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP73" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP73" s="3"/>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -17145,12 +17153,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ73" s="3"/>
+      <c r="AZ73" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26宿迁交通MTN003</t>
+          <t>26中石油MTN002(科创债)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17160,64 +17170,64 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>102684073.IB</t>
+          <t>102684065.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3.36</v>
+        <v>50.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3.36</v>
+        <v>50.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>35.85</v>
+        <v>16.71</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>25宿迁交通MTN003</t>
+          <t>24中石油MTN001</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>3.82Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.6880</t>
+          <t>1.5608</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>--/1.6600</t>
+          <t>1.5800/--</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>宿迁市交通产业集团有限公司</t>
+          <t>中国石油天然气集团有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C- 16.38</t>
+          <t>C- 20.69</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17232,7 +17242,7 @@
       </c>
       <c r="S74" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T74" s="3" t="inlineStr">
@@ -17241,40 +17251,44 @@
         </is>
       </c>
       <c r="U74" s="4" t="n">
-        <v>3.8393</v>
+        <v>1.084</v>
       </c>
       <c r="V74" s="4" t="n">
-        <v>1.24</v>
+        <v>1.0</v>
       </c>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z74" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具募集资金3.36亿元,拟全部用于偿还存量债务融资工具本金[24宿迁交通MTN005]</t>
+          <t>本期中期票据拟募集资金50亿元,募集资金最终用于发行人科技创新及主营业务生产经营</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>中国工商银行股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
@@ -17285,7 +17299,7 @@
       </c>
       <c r="AF74" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG74" s="3" t="inlineStr">
@@ -17295,7 +17309,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>宿迁市交通产业集团有限公司2026年度第三期中期票据</t>
+          <t>中国石油天然气集团有限公司2026年度第二期科技创新债券</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17305,14 +17319,10 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK74" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-19</t>
+        </is>
+      </c>
+      <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -17330,32 +17340,32 @@
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>其他石油石化</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
@@ -17383,14 +17393,12 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ74" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ74" s="3"/>
     </row>
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26国新保理SCP008</t>
+          <t>26桂投资MTN002</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -17400,64 +17408,64 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>012682465.IB</t>
+          <t>102684075.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>11.8</v>
+        <v>3.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>11.8</v>
+        <v>5.0</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.90 ~ 2.40</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>35.18</v>
+        <v>68.85</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>25国保02</t>
+          <t>26桂投资MTN001</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>280D</t>
+          <t>4.88Y+N</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.5232</t>
+          <t>2.1976</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司</t>
+          <t>广西投资集团有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>B- 41.35</t>
+          <t>C 28.84</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17480,16 +17488,18 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U75" s="3"/>
+      <c r="U75" s="4" t="n">
+        <v>5.5</v>
+      </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -17500,28 +17510,28 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本次发行11.8亿元拟用于偿还有息负债[26国新保理SCP001]</t>
+          <t>发行待偿还余额不超过5亿元的有息债务，募集资金全部用于发行人本部到期的短期流贷</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
@@ -17531,7 +17541,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司2026年度第八期超短期融资券</t>
+          <t>广西投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17541,10 +17551,14 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
-        </is>
-      </c>
-      <c r="AK75" s="3"/>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK75" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL75" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -17562,28 +17576,32 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP75" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17598,12 +17616,12 @@
       </c>
       <c r="AW75" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX75" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY75" s="3" t="inlineStr">
@@ -17612,23 +17630,23 @@
         </is>
       </c>
       <c r="AZ75" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26中石油MTN002(科创债)</t>
+          <t>26浙交投MTN007</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>10-16 18:00</t>
+          <t>10-16 17:00</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>102684065.IB</t>
+          <t>102684057.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -17637,14 +17655,14 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
@@ -17655,37 +17673,37 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>24中石油MTN001</t>
+          <t>24浙交投MTN001</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.5608</t>
+          <t>1.6649</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.5800/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司</t>
+          <t>浙江省交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C- 20.69</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17695,12 +17713,12 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 14:00</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T76" s="3" t="inlineStr">
@@ -17709,19 +17727,19 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>1.084</v>
+        <v>2.67</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.63%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -17729,24 +17747,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z76" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟募集资金50亿元,募集资金最终用于发行人科技创新及主营业务生产经营</t>
+          <t>本期中期票据募集资金10亿元将全部用于偿还发行人和下属子公司有息债务本息</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
@@ -17757,7 +17771,7 @@
       </c>
       <c r="AF76" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG76" s="3" t="inlineStr">
@@ -17767,7 +17781,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司2026年度第二期科技创新债券</t>
+          <t>浙江省交通投资集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17798,32 +17812,32 @@
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>其他石油石化</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
@@ -17856,7 +17870,7 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26桂投资MTN002</t>
+          <t>26兵器MTN004(科创债)</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -17866,64 +17880,64 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>102684075.IB</t>
+          <t>102684058.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.40</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>68.85</v>
+        <v>18.85</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>26桂投资MTN001</t>
+          <t>26兵器K1</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>4.88Y+N</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>2.1976</t>
+          <t>1.6081</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司</t>
+          <t>中国兵器工业集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C 28.84</t>
+          <t>B- 43.58</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -17947,17 +17961,19 @@
         </is>
       </c>
       <c r="U77" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V77" s="3"/>
+        <v>2.1</v>
+      </c>
+      <c r="V77" s="4" t="n">
+        <v>1.3</v>
+      </c>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
@@ -17968,17 +17984,17 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>发行待偿还余额不超过5亿元的有息债务，募集资金全部用于发行人本部到期的短期流贷</t>
+          <t>发行人本期科技创新债券发行规模20亿元,募集资金拟用于偿还发行人有息负债。</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,广西北部湾银行股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国建设银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
@@ -17989,7 +18005,7 @@
       </c>
       <c r="AF77" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG77" s="3" t="inlineStr">
@@ -17999,7 +18015,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>广西投资集团有限公司2026年度第二期中期票据</t>
+          <t>中国兵器工业集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -18039,29 +18055,29 @@
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
+          <t>其他设备制造</t>
+        </is>
+      </c>
+      <c r="AR77" s="3" t="inlineStr">
+        <is>
+          <t>军工设备</t>
+        </is>
+      </c>
+      <c r="AS77" s="3" t="inlineStr">
+        <is>
+          <t>军工设备</t>
+        </is>
+      </c>
+      <c r="AT77" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR77" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS77" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT77" s="3" t="inlineStr">
-        <is>
-          <t>工业金属</t>
-        </is>
-      </c>
       <c r="AU77" s="3" t="inlineStr">
         <is>
           <t/>
@@ -18074,12 +18090,12 @@
       </c>
       <c r="AW77" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX77" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY77" s="3" t="inlineStr">
@@ -18087,81 +18103,79 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ77" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ77" s="3"/>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26浙交投MTN007</t>
+          <t>26中建一局SCP008</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>10-16 17:00</t>
+          <t>10-16 18:00</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>102684057.IB</t>
+          <t>012682467.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.25 ~ 1.45</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16.71</v>
+        <v>12.34</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>24浙交投MTN001</t>
+          <t>26中建一局SCP003</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>98D</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.6649</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>1.4800/--</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司</t>
+          <t>中国建筑一局(集团)有限公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>B- 41.03</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18171,12 +18185,12 @@
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>10-16 14:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T78" s="3" t="inlineStr">
@@ -18185,19 +18199,19 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>2.67</v>
+        <v>1.22</v>
       </c>
       <c r="V78" s="4" t="n">
-        <v>1.06</v>
+        <v>1.0</v>
       </c>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.42%~1.46%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
@@ -18208,28 +18222,28 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金10亿元将全部用于偿还发行人和下属子公司有息债务本息</t>
+          <t>发行人本期债务融资工具发行金额5亿元，所募集资金拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
       <c r="AE78" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF78" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG78" s="3" t="inlineStr">
@@ -18239,7 +18253,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>浙江省交通投资集团有限公司2026年度第七期中期票据</t>
+          <t>中国建筑一局(集团)有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -18249,7 +18263,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2029-10-19</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="AK78" s="3"/>
@@ -18270,32 +18284,32 @@
       </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT78" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU78" s="3" t="inlineStr">
@@ -18328,7 +18342,7 @@
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26兵器MTN004(科创债)</t>
+          <t>26华能集MTN002</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18338,12 +18352,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>102684058.IB</t>
+          <t>102684068.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>20Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -18354,48 +18368,48 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>2.00 ~ 2.50</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>18.85</v>
+        <v>10.09</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>26兵器K1</t>
+          <t>26华能集MTN001</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>19.83Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.6081</t>
+          <t>2.1766</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>2.1700/2.1675</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司</t>
+          <t>中国华能集团有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>B- 43.58</t>
+          <t>B- 40.61</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18410,7 +18424,7 @@
       </c>
       <c r="S79" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="T79" s="3" t="inlineStr">
@@ -18419,11 +18433,9 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V79" s="4" t="n">
-        <v>1.3</v>
-      </c>
+        <v>3.65</v>
+      </c>
+      <c r="V79" s="3"/>
       <c r="W79" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -18431,7 +18443,7 @@
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -18439,20 +18451,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z79" s="3"/>
+      <c r="Z79" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券发行规模20亿元,募集资金拟用于偿还发行人有息负债。</t>
+          <t>本期债务融资工具拟募集资金20亿元,用于偿还公司本部到期债务</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国建设银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>招商银行股份有限公司,长城证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
@@ -18473,7 +18489,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司2026年度第四期科技创新债券</t>
+          <t>中国华能集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18483,14 +18499,10 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK79" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2046-10-19</t>
+        </is>
+      </c>
+      <c r="AK79" s="3"/>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t>2026-10-20</t>
@@ -18518,22 +18530,22 @@
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>军工设备</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>军工设备</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18566,7 +18578,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26中建一局SCP008</t>
+          <t>26国能江苏SCP009</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18576,64 +18588,64 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>012682467.IB</t>
+          <t>012682466.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.68Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.45</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>12.34</v>
+        <v>23.18</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26中建一局SCP003</t>
+          <t>26国能江苏SCP007</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>98D</t>
+          <t>193D</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.4545</t>
+          <t>1.4796</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.4800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>中国建筑一局(集团)有限公司</t>
+          <t>国家能源集团江苏电力有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>B- 41.03</t>
+          <t>C- 17.97</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18648,7 +18660,7 @@
       </c>
       <c r="S80" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr">
@@ -18657,19 +18669,17 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.42%~1.46%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18680,17 +18690,17 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额5亿元，所募集资金拟用于偿还有息债务</t>
+          <t>本期超短期融资券发行金额2.00亿元,全部用于归还存量到期债务以及补充营运资金。</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
@@ -18711,7 +18721,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>中国建筑一局(集团)有限公司2026年度第八期超短期融资券</t>
+          <t>国家能源集团江苏电力有限公司2026年度第九期超短期融资券</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18721,7 +18731,7 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-06-23</t>
         </is>
       </c>
       <c r="AK80" s="3"/>
@@ -18747,27 +18757,27 @@
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18795,79 +18805,77 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ80" s="3"/>
+      <c r="AZ80" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26华能集MTN002</t>
+          <t>26银河证券CP013</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>10-16 18:00</t>
+          <t>10-16 17:15</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>102684068.IB</t>
+          <t>072610202.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>20Y</t>
+          <t>0.5Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>2.00 ~ 2.50</t>
-        </is>
-      </c>
+        <v>40.0</v>
+      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="4" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>10.09</v>
+        <v>31.13</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26华能集MTN001</t>
+          <t>26银河证券CP011</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>19.83Y</t>
+          <t>152D</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>2.1766</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>2.1700/2.1675</t>
+          <t>1.5000/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>中国华能集团有限公司</t>
+          <t>中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>B- 40.61</t>
+          <t>B- 45.11</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18882,7 +18890,7 @@
       </c>
       <c r="S81" s="3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr">
@@ -18890,18 +18898,16 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U81" s="4" t="n">
-        <v>3.65</v>
-      </c>
+      <c r="U81" s="3"/>
       <c r="V81" s="3"/>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -18909,35 +18915,27 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z81" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
-        </is>
-      </c>
-      <c r="AB81" s="3" t="inlineStr">
-        <is>
-          <t>本期债务融资工具拟募集资金20亿元,用于偿还公司本部到期债务</t>
-        </is>
-      </c>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB81" s="3"/>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,长城证券股份有限公司,中信银行股份有限公司</t>
+          <t>中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
       <c r="AE81" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF81" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG81" s="3" t="inlineStr">
@@ -18947,7 +18945,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>中国华能集团有限公司2026年度第二期中期票据</t>
+          <t>中国银河证券股份有限公司2026年度第十三期短期融资券</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -18957,7 +18955,7 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2046-10-19</t>
+          <t>2027-04-21</t>
         </is>
       </c>
       <c r="AK81" s="3"/>
@@ -18968,7 +18966,7 @@
       </c>
       <c r="AM81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AN81" s="3" t="inlineStr">
@@ -18978,32 +18976,32 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -19036,7 +19034,7 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26国能江苏SCP009</t>
+          <t>26中交投MTN004A</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -19046,49 +19044,49 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>012682466.IB</t>
+          <t>102684061.IB</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>0.68Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>23.18</v>
+        <v>37.53</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>26国能江苏SCP007</t>
+          <t>25中交投MTN002B</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>193D</t>
+          <t>1.81Y+N</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.4796</t>
+          <t>1.6513</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -19098,12 +19096,12 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团江苏电力有限公司</t>
+          <t>中交投资有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C- 17.97</t>
+          <t>C- 18.43</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19113,12 +19111,12 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 15:00</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr">
@@ -19127,17 +19125,17 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
@@ -19145,26 +19143,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z82" s="3"/>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额2.00亿元,全部用于归还存量到期债务以及补充营运资金。</t>
+          <t>本期中期票据基础发行金额为0亿元，发行金额上限为12.00亿元，拟全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>申万宏源证券有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF82" s="3" t="inlineStr">
@@ -19179,7 +19181,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>国家能源集团江苏电力有限公司2026年度第九期超短期融资券</t>
+          <t>中交投资有限公司2026年度第四期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19189,7 +19191,7 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2027-06-23</t>
+          <t>2028-10-19</t>
         </is>
       </c>
       <c r="AK82" s="3"/>
@@ -19215,27 +19217,27 @@
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19250,12 +19252,12 @@
       </c>
       <c r="AW82" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX82" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY82" s="3" t="inlineStr">
@@ -19263,77 +19265,79 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AZ82" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ82" s="3"/>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26银河证券CP013</t>
+          <t>26石油K1</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>10-16 17:15</t>
+          <t>10-16 18:30</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>072610202.IB</t>
+          <t>246213.SH</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>0.5Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G83" s="3"/>
+        <v>50.0</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.75</t>
+        </is>
+      </c>
       <c r="H83" s="4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>31.13</v>
+        <v>12.85</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>26银河证券CP011</t>
+          <t>25中石油MTN002(科创债)</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>152D</t>
+          <t>4.06Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.5810</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.5000/--</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
+          <t>中国石油天然气集团有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>B- 45.11</t>
+          <t>C- 20.69</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19343,7 +19347,7 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>10-16 09:00</t>
+          <t>10-16 15:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -19356,16 +19360,18 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="U83" s="3"/>
+      <c r="U83" s="4" t="n">
+        <v>3.644</v>
+      </c>
       <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -19373,37 +19379,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z83" s="3"/>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA83" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
         </is>
       </c>
-      <c r="AB83" s="3"/>
+      <c r="AB83" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行规模不超过50亿元(含50亿元),募集资金拟用于发行人生产性支出,包括但不限于偿还债务、补充流动资金、项目建设等,募集资金将部分用于算力等领域相关项目建设等用途</t>
+        </is>
+      </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
       <c r="AE83" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司2026年度第十三期短期融资券</t>
+          <t>中国石油天然气集团有限公司2026年面向专业投资者公开发行科技创新公司债券(数字人民币)(算力+能源)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19413,53 +19427,57 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2027-04-21</t>
-        </is>
-      </c>
-      <c r="AK83" s="3"/>
+          <t>2031-10-19</t>
+        </is>
+      </c>
+      <c r="AK83" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t/>
         </is>
       </c>
       <c r="AM83" s="3" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AN83" s="3" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AN83" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他石油石化</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
@@ -19492,7 +19510,7 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26中交投MTN004A</t>
+          <t>26中石油MTN001(科创债)</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19502,49 +19520,49 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>102684061.IB</t>
+          <t>102684072.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>6.0</v>
+        <v>50.0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>4.0</v>
+        <v>50.0</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>37.53</v>
+        <v>16.71</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>25中交投MTN002B</t>
+          <t>24中石油MTN001</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>1.81Y+N</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.6513</t>
+          <t>1.5608</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -19554,12 +19572,12 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司</t>
+          <t>中国石油天然气集团有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>C- 18.43</t>
+          <t>C- 20.69</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19569,12 +19587,12 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>10-16 15:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T84" s="3" t="inlineStr">
@@ -19583,17 +19601,17 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>3.92</v>
+        <v>1.168</v>
       </c>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.53%~1.63%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
@@ -19613,12 +19631,12 @@
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行金额为0亿元，发行金额上限为12.00亿元，拟全部用于偿还发行人有息债务。</t>
+          <t>本期中期票据拟募集资金50亿元,募集资金最终用于发行人科技创新及主营业务生产经营</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,招商银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国建设银行股份有限公司,中国农业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19629,7 +19647,7 @@
       </c>
       <c r="AF84" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG84" s="3" t="inlineStr">
@@ -19639,7 +19657,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司2026年度第四期中期票据(品种一)</t>
+          <t>中国石油天然气集团有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19649,7 +19667,7 @@
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2028-10-19</t>
+          <t>2029-10-19</t>
         </is>
       </c>
       <c r="AK84" s="3"/>
@@ -19675,27 +19693,27 @@
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>其他石油石化</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19710,12 +19728,12 @@
       </c>
       <c r="AW84" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX84" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY84" s="3" t="inlineStr">
@@ -19728,74 +19746,74 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26石油K1</t>
+          <t>26浙国贸SCP004</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>10-16 18:30</t>
+          <t>10-16 18:00</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>246213.SH</t>
+          <t>012682460.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>25.0</v>
+        <v>4.0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>50.0</v>
+        <v>4.0</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.75</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>12.85</v>
+        <v>22.18</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>25中石油MTN002(科创债)</t>
+          <t>24浙国贸MTN001</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>4.06Y</t>
+          <t>157D</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.5810</t>
+          <t>1.4886</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司</t>
+          <t>浙江省国际贸易集团有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 20.69</t>
+          <t>C 27.57</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19805,12 +19823,12 @@
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>10-16 15:00</t>
+          <t>10-16 09:00</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T85" s="3" t="inlineStr">
@@ -19819,17 +19837,17 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>3.644</v>
+        <v>2.75</v>
       </c>
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
@@ -19837,45 +19855,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z85" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过50亿元(含50亿元),募集资金拟用于发行人生产性支出,包括但不限于偿还债务、补充流动资金、项目建设等,募集资金将部分用于算力等领域相关项目建设等用途</t>
+          <t>本期超短期融资券发行金额4亿元，募集资金拟用于偿还发行人即将到期的债务融资工具本金[26浙国贸SCP001]</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD85" s="3"/>
       <c r="AE85" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF85" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG85" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>中国石油天然气集团有限公司2026年面向专业投资者公开发行科技创新公司债券(数字人民币)(算力+能源)(第一期)(品种一)</t>
+          <t>浙江省国际贸易集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19885,22 +19899,18 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2031-10-19</t>
-        </is>
-      </c>
-      <c r="AK85" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-07-16</t>
+        </is>
+      </c>
+      <c r="AK85" s="3"/>
       <c r="AL85" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AM85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AN85" s="3" t="inlineStr">
@@ -19915,27 +19925,27 @@
       </c>
       <c r="AP85" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>其他石油石化</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
